--- a/江苏省环评单位_官网及公示入口.xlsx
+++ b/江苏省环评单位_官网及公示入口.xlsx
@@ -454,14 +454,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>江苏省环评受理单位：官网及环评公示入口</t>
+          <t>江苏省环评单位：官网及环评公示入口</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>单位来自江苏省环评单位.csv（13 市 88148 条环评受理记录清洗归并）。四个入口列固定；没有分设栏目的，混合入口重复填在相关列并在备注注明。「其他部门」按约定只给主页。生成于 2026-09-21。</t>
+          <t>单位来自 江苏省环评单位.csv（13 市、84168 条环评受理记录清洗归并）。四个入口列固定；没有分设栏目的，混合入口重复填在相关列并在备注注明。「其他部门」按约定只给主页。生成于 2026-09-21。</t>
         </is>
       </c>
     </row>
